--- a/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -517,7 +517,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Confermata esistenza e operatività (fininfo.hr: attiva dal 1999, rating A+ 2026, fatturato ~6,25 Mln HRK nel 2025). Rivenditore generalista ferramenta/edilizia (Strossmayerova 4, Virovitica) con attività registrata che include esplicitamente metallo e prodotti metallici, oltre a utensili elettrici, tubi e lamiere: considerato distributore borderline ma rilevante per il settore metalworking. Telefono ed email verificati su fininfo.hr (registro imprese); email è nominale del direttore Mario Bobanac, non un indirizzo generico aziendale. I due numeri di negozio riportati nella lista grezza (033 721 331 / 033 722 038) non hanno trovato conferma diretta in questa verifica.</t>
+          <t>Confermata esistenza e operatività (fininfo.hr: attiva dal 1999, rating A+ 2026, fatturato ~6,25 Mln HRK nel 2025). Rivenditore generalista ferramenta/edilizia (Strossmayerova 4, Virovitica) con attività registrata che include esplicitamente metallo e prodotti metallici, oltre a utensili elettrici, tubi e lamiere: considerato distributore borderline ma rilevante per il settore metalworking. Telefono ed email verificati su fininfo.hr (registro imprese); email è nominale del direttore Mario Bobanac, non un indirizzo generico aziendale. I due numeri di negozio riportati nella lista grezza (033 721 331 / 033 722 038) non hanno trovato conferma diretta in questa verifica. [DUPLICATO — vedi anche: 2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">

--- a/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-15_02_Croazia_Virovitico-podravska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Confermata esistenza e operatività (attiva dal 1990, sede Ulica Franje Fujsa 39, 33000 Virovitica, punto vendita anche in Strossmayerova/Stromajerova 11). Rivenditore di ferro, tondino/armature, tubi, profilati e lamiere, con linea dedicata a elettrodi e leghe per saldatura/brasatura (legure za lemljenje, zavarivanje): consumabili direttamente pertinenti al settore metalworking. Dati confermati da fonti multiple indipendenti (Kompass, zutestranice.hr, ricerca web) coerenti con quelli forniti dal ricercatore (telefono ed email confermati).</t>
+          <t>Confermata esistenza e operatività (attiva dal 1990, sede Ulica Franje Fujsa 39, 33000 Virovitica, punto vendita anche in Strossmayerova/Stromajerova 11). Rivenditore di ferro, tondino/armature, tubi, profilati e lamiere, con linea dedicata a elettrodi e leghe per saldatura/brasatura (legure za lemljenje, zavarivanje): consumabili direttamente pertinenti al settore metalworking. Dati confermati da fonti multiple indipendenti (Kompass, zutestranice.hr, ricerca web) coerenti con quelli forniti dal ricercatore (telefono ed email confermati). [DUPLICATO — vedi anche: 2026-09-15_01_Croazia_Virovitico-podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
